--- a/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0FCE104-8AD0-419C-96A6-8DDC26B33478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{540DC583-7C32-4983-AB0C-DABFE2B17623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -731,10 +731,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,FaD,RaD,FaP,SaP,WaP,SaD,RaP</t>
+    <t>RaP,SaD,WaD,FaD,RaD,FaP,SaP,WaP</t>
   </si>
   <si>
-    <t>RaP,SaN,WaN,FaN,RaN,FaP,SaP,WaP</t>
+    <t>FaP,SaP,FaN,SaN,WaN,WaP,RaP,RaN</t>
   </si>
 </sst>
 </file>
@@ -24359,7 +24359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6365D449-E4D4-4083-A67B-A7D1F8DFEB7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AF8727-B12C-4641-B650-D9D0D98EA5E8}">
   <dimension ref="A9:AN20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24697,7 +24697,7 @@
         <v>155</v>
       </c>
       <c r="AM13">
-        <v>0.19272847718019148</v>
+        <v>0.19272847718019145</v>
       </c>
       <c r="AN13" t="s">
         <v>198</v>
@@ -24975,7 +24975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E44ED13F-CB68-4AAD-84E3-08158B30B8EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE78776-DE0D-49CD-9103-AFDEE645D8A6}">
   <dimension ref="A9:AN130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25785,7 +25785,7 @@
         <v>204</v>
       </c>
       <c r="AM18">
-        <v>0.18889259227055935</v>
+        <v>0.18889259227055941</v>
       </c>
       <c r="AN18" t="s">
         <v>198</v>
@@ -26025,7 +26025,7 @@
         <v>202</v>
       </c>
       <c r="AM21">
-        <v>0.1231374405446225</v>
+        <v>0.12313744054462249</v>
       </c>
       <c r="AN21" t="s">
         <v>198</v>

--- a/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{540DC583-7C32-4983-AB0C-DABFE2B17623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7680018-A3B4-4581-A299-233E31065BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -731,10 +731,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaP,SaD,WaD,FaD,RaD,FaP,SaP,WaP</t>
+    <t>FaD,RaD,RaP,FaP,SaP,WaD,SaD,WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,FaN,SaN,WaN,WaP,RaP,RaN</t>
+    <t>RaP,SaN,WaN,FaN,FaP,SaP,RaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24359,7 +24359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AF8727-B12C-4641-B650-D9D0D98EA5E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7688C6-288F-4A16-B93F-A566591C1FB2}">
   <dimension ref="A9:AN20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24588,7 +24588,7 @@
         <v>155</v>
       </c>
       <c r="AM11">
-        <v>0.1799960784130826</v>
+        <v>0.17999607841308263</v>
       </c>
       <c r="AN11" t="s">
         <v>198</v>
@@ -24697,7 +24697,7 @@
         <v>155</v>
       </c>
       <c r="AM13">
-        <v>0.19272847718019145</v>
+        <v>0.19272847718019151</v>
       </c>
       <c r="AN13" t="s">
         <v>198</v>
@@ -24975,7 +24975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE78776-DE0D-49CD-9103-AFDEE645D8A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B61C46A-95BA-4F72-A8A2-75BFA559B138}">
   <dimension ref="A9:AN130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25204,7 +25204,7 @@
         <v>199</v>
       </c>
       <c r="AM11">
-        <v>0.10378861312113491</v>
+        <v>0.1037886131211349</v>
       </c>
       <c r="AN11" t="s">
         <v>198</v>
@@ -25785,7 +25785,7 @@
         <v>204</v>
       </c>
       <c r="AM18">
-        <v>0.18889259227055941</v>
+        <v>0.18889259227055935</v>
       </c>
       <c r="AN18" t="s">
         <v>198</v>
@@ -26025,7 +26025,7 @@
         <v>202</v>
       </c>
       <c r="AM21">
-        <v>0.12313744054462249</v>
+        <v>0.1231374405446225</v>
       </c>
       <c r="AN21" t="s">
         <v>198</v>

--- a/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7680018-A3B4-4581-A299-233E31065BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B50E5FB-3A4D-4CC4-A01E-B33F6357C4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -731,10 +731,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,RaD,RaP,FaP,SaP,WaD,SaD,WaP</t>
+    <t>SaD,WaP,RaD,FaP,SaP,FaD,RaP,WaD</t>
   </si>
   <si>
-    <t>RaP,SaN,WaN,FaN,FaP,SaP,RaN,WaP</t>
+    <t>FaP,SaP,WaP,SaN,WaN,FaN,RaN,RaP</t>
   </si>
 </sst>
 </file>
@@ -24359,7 +24359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7688C6-288F-4A16-B93F-A566591C1FB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942FDF1C-0778-4BCD-B6CF-2E599F87B780}">
   <dimension ref="A9:AN20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24588,7 +24588,7 @@
         <v>155</v>
       </c>
       <c r="AM11">
-        <v>0.17999607841308263</v>
+        <v>0.1799960784130826</v>
       </c>
       <c r="AN11" t="s">
         <v>198</v>
@@ -24697,7 +24697,7 @@
         <v>155</v>
       </c>
       <c r="AM13">
-        <v>0.19272847718019151</v>
+        <v>0.19272847718019148</v>
       </c>
       <c r="AN13" t="s">
         <v>198</v>
@@ -24975,7 +24975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B61C46A-95BA-4F72-A8A2-75BFA559B138}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D0D00D-8A4A-42A8-909D-3AA1DA5D6476}">
   <dimension ref="A9:AN130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25204,7 +25204,7 @@
         <v>199</v>
       </c>
       <c r="AM11">
-        <v>0.1037886131211349</v>
+        <v>0.10378861312113491</v>
       </c>
       <c r="AN11" t="s">
         <v>198</v>

--- a/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B50E5FB-3A4D-4CC4-A01E-B33F6357C4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E019DEC-C2D9-4AAA-B044-E0A9B9D8DDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -731,10 +731,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,WaP,RaD,FaP,SaP,FaD,RaP,WaD</t>
+    <t>WaD,RaD,WaP,FaD,FaP,SaP,SaD,RaP</t>
   </si>
   <si>
-    <t>FaP,SaP,WaP,SaN,WaN,FaN,RaN,RaP</t>
+    <t>FaN,RaN,SaN,WaN,RaP,WaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24359,7 +24359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942FDF1C-0778-4BCD-B6CF-2E599F87B780}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25889EE0-A709-448F-8A38-D3074EDAACA5}">
   <dimension ref="A9:AN20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24647,7 +24647,7 @@
         <v>155</v>
       </c>
       <c r="AM12">
-        <v>0.18745518371456693</v>
+        <v>0.1874551837145669</v>
       </c>
       <c r="AN12" t="s">
         <v>198</v>
@@ -24975,7 +24975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D0D00D-8A4A-42A8-909D-3AA1DA5D6476}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A925DC90-E898-4A6A-96CD-D29F33E62615}">
   <dimension ref="A9:AN130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25204,7 +25204,7 @@
         <v>199</v>
       </c>
       <c r="AM11">
-        <v>0.10378861312113491</v>
+        <v>0.1037886131211349</v>
       </c>
       <c r="AN11" t="s">
         <v>198</v>

--- a/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E019DEC-C2D9-4AAA-B044-E0A9B9D8DDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D919109-56BE-4935-AE48-5A1B9612DEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -731,10 +731,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,RaD,WaP,FaD,FaP,SaP,SaD,RaP</t>
+    <t>RaD,WaD,FaD,SaD,RaP,FaP,SaP,WaP</t>
   </si>
   <si>
-    <t>FaN,RaN,SaN,WaN,RaP,WaP,FaP,SaP</t>
+    <t>RaP,FaP,SaP,FaN,RaN,WaP,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24359,7 +24359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25889EE0-A709-448F-8A38-D3074EDAACA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106A75EB-1BBD-45AC-910A-0332195E4371}">
   <dimension ref="A9:AN20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24647,7 +24647,7 @@
         <v>155</v>
       </c>
       <c r="AM12">
-        <v>0.1874551837145669</v>
+        <v>0.18745518371456693</v>
       </c>
       <c r="AN12" t="s">
         <v>198</v>
@@ -24975,7 +24975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A925DC90-E898-4A6A-96CD-D29F33E62615}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F886C22-3D62-4335-B370-F305E7A94BC8}">
   <dimension ref="A9:AN130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25204,7 +25204,7 @@
         <v>199</v>
       </c>
       <c r="AM11">
-        <v>0.1037886131211349</v>
+        <v>0.10378861312113491</v>
       </c>
       <c r="AN11" t="s">
         <v>198</v>
@@ -25785,7 +25785,7 @@
         <v>204</v>
       </c>
       <c r="AM18">
-        <v>0.18889259227055935</v>
+        <v>0.18889259227055941</v>
       </c>
       <c r="AN18" t="s">
         <v>198</v>
